--- a/linkage/data_processing_elements_linkage-NHANES11.xlsx
+++ b/linkage/data_processing_elements_linkage-NHANES11.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Melchias\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93066499-106A-44D2-AC41-A78AFC7C907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C56790AD-5F29-40FF-AEE7-6E9BB633D11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
   <si>
     <t>index</t>
   </si>
@@ -212,9 +212,6 @@
     <t>unavailable</t>
   </si>
   <si>
-    <t>incompatible</t>
-  </si>
-  <si>
     <t>internal_comment</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
   </si>
   <si>
     <t>__BLANK__</t>
-  </si>
-  <si>
-    <t>undetermined</t>
   </si>
   <si>
     <t>Change to "unavailable" if confirmed.
@@ -262,9 +256,6 @@
     <t>recode(1=0; 2=1; 3=0; 4=0; 5=0; 6=0; 7=0; 8=0; 9=0; 10=1; ELSE=NA)</t>
   </si>
   <si>
-    <t>The category "Malignant neoplasms" is recoded with others.</t>
-  </si>
-  <si>
     <t>Change to "impossible" if confirmed.
 Variable in the data dictionnary, but not in dataset (as of 2026-08-12).
 Variable is DODYEAR with label "Year of Death: NHIS only" for death after 18 years old, so it may not be available.</t>
@@ -277,13 +268,28 @@
   </si>
   <si>
     <t>dataset_NHANES11</t>
+  </si>
+  <si>
+    <t>comment_question_for_cohort</t>
+  </si>
+  <si>
+    <t>validation_comment</t>
+  </si>
+  <si>
+    <t>Checked against NCIS linked mortality files (LMFs), and the variables dodqtr and dodyear are present but all NA, so consider these unavailable.</t>
+  </si>
+  <si>
+    <t>The study-specific category "Malignant neoplasms" is recoded as DataSchema variable "All Other Causes NHANES" category 1 = Yes.</t>
+  </si>
+  <si>
+    <t>Can we confirm that there is no information about date of death available?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,37 +298,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -331,23 +310,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -362,42 +354,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,11 +717,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A96D0D0-036F-4639-8FBF-4A4CEF797E7C}">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" style="4" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="85.42578125" style="5" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" style="5" customWidth="1"/>
@@ -749,79 +733,88 @@
     <col min="11" max="11" width="27.5703125" style="5" customWidth="1"/>
     <col min="12" max="12" width="17.5703125" style="5" customWidth="1"/>
     <col min="13" max="13" width="27.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="24.42578125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="57.42578125" style="5" customWidth="1"/>
-    <col min="19" max="16384" width="11.5703125" style="5"/>
+    <col min="14" max="14" width="24.42578125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="18.85546875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="57.42578125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="22.28515625" style="4" customWidth="1"/>
+    <col min="20" max="20" width="29.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.28515625" style="4" customWidth="1"/>
+    <col min="22" max="16384" width="11.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="S1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>76</v>
+      <c r="B2" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>37</v>
@@ -833,30 +826,30 @@
         <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="R2" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>76</v>
+      <c r="B3" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>18</v>
@@ -868,33 +861,33 @@
         <v>17</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>76</v>
+      <c r="B4" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>20</v>
@@ -906,36 +899,42 @@
         <v>17</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="11" t="s">
+      <c r="P4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="S4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="S4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>76</v>
+      <c r="B5" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -947,30 +946,42 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="O5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>76</v>
+      <c r="B6" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>42</v>
@@ -982,35 +993,35 @@
         <v>17</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="R6" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1020,38 +1031,38 @@
         <v>17</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="P7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q7" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="Q7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1061,38 +1072,38 @@
         <v>17</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="R8" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+    </row>
+    <row r="9" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1102,36 +1113,36 @@
         <v>17</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="P9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="Q9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>76</v>
+      <c r="B10" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
@@ -1143,38 +1154,38 @@
         <v>17</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
+      <c r="Q10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1184,38 +1195,38 @@
         <v>17</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="P11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q11" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
+      <c r="Q11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1225,38 +1236,38 @@
         <v>17</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="P12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q12" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R12" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
+      <c r="Q12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1266,38 +1277,38 @@
         <v>17</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="M13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O13" s="5" t="s">
+      <c r="O13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q13" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R13" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
+      <c r="Q13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1307,36 +1318,36 @@
         <v>17</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="M14" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="O14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="P14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q14" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R14" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
+      <c r="Q14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>76</v>
+      <c r="B15" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>25</v>
@@ -1348,33 +1359,32 @@
         <v>17</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O15" s="5" t="s">
+      <c r="N15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P15" s="12" t="s">
+      <c r="P15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q15" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>72</v>
+      <c r="Q15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R15" xr:uid="{2A96D0D0-036F-4639-8FBF-4A4CEF797E7C}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/linkage/data_processing_elements_linkage-NHANES11.xlsx
+++ b/linkage/data_processing_elements_linkage-NHANES11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C56790AD-5F29-40FF-AEE7-6E9BB633D11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1225266-3537-44C6-8B5B-E0A79E170672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$R$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$R$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="107">
   <si>
     <t>index</t>
   </si>
@@ -253,9 +253,6 @@
     <t>recode(1=0; 2=0; 3=0; 4=1; 5=0; 6=0; 7=0; 8=0; 9=0; 10=0; ELSE=NA)</t>
   </si>
   <si>
-    <t>recode(1=0; 2=1; 3=0; 4=0; 5=0; 6=0; 7=0; 8=0; 9=0; 10=1; ELSE=NA)</t>
-  </si>
-  <si>
     <t>Change to "impossible" if confirmed.
 Variable in the data dictionnary, but not in dataset (as of 2026-08-12).
 Variable is DODYEAR with label "Year of Death: NHIS only" for death after 18 years old, so it may not be available.</t>
@@ -264,38 +261,130 @@
     <t>ucod_leading</t>
   </si>
   <si>
-    <t>harmonized_dataset_NHANES11</t>
-  </si>
-  <si>
-    <t>dataset_NHANES11</t>
-  </si>
-  <si>
     <t>comment_question_for_cohort</t>
   </si>
   <si>
     <t>validation_comment</t>
   </si>
   <si>
-    <t>Checked against NCIS linked mortality files (LMFs), and the variables dodqtr and dodyear are present but all NA, so consider these unavailable.</t>
-  </si>
-  <si>
-    <t>The study-specific category "Malignant neoplasms" is recoded as DataSchema variable "All Other Causes NHANES" category 1 = Yes.</t>
-  </si>
-  <si>
-    <t>Can we confirm that there is no information about date of death available?</t>
+    <t>dataset_linkage_mortality_NHANES11</t>
+  </si>
+  <si>
+    <t>harmonized_dataset_linkage_mortality_NHANES11</t>
+  </si>
+  <si>
+    <t>dth_cancer_nhanes</t>
+  </si>
+  <si>
+    <t>Malignant neoplasms NHANES - ICD10: C00-C97</t>
+  </si>
+  <si>
+    <t>recode(1=0; 2=1; 3=0; 4=0; 5=0; 6=0; 7=0; 8=0; 9=0; 10=0; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>adm_study_id</t>
+  </si>
+  <si>
+    <t>Study identifier</t>
+  </si>
+  <si>
+    <t>Acronym of the study</t>
+  </si>
+  <si>
+    <t>adm_dataset_id</t>
+  </si>
+  <si>
+    <t>Study dataset identifier</t>
+  </si>
+  <si>
+    <t>Identifier of the study population</t>
+  </si>
+  <si>
+    <t>adm_country</t>
+  </si>
+  <si>
+    <t>Study country</t>
+  </si>
+  <si>
+    <t>Country of study</t>
+  </si>
+  <si>
+    <t>adm_collect_year</t>
+  </si>
+  <si>
+    <t>Data collection time - Year</t>
+  </si>
+  <si>
+    <t>adm_collect_month</t>
+  </si>
+  <si>
+    <t>Data collection time - Month</t>
+  </si>
+  <si>
+    <t>dth_status</t>
+  </si>
+  <si>
+    <t>Death status</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is deceased</t>
+  </si>
+  <si>
+    <t>mortstat</t>
+  </si>
+  <si>
+    <t>Final Mortality Status</t>
+  </si>
+  <si>
+    <t>recode(1=0; 2=0; 3=0; 4=0; 5=0; 6=0; 7=0; 8=0; 9=0; 10=1; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>0 = Assumed alive
+1 = Assumed deceased
+&lt;NA&gt; = Ineligible or under age 18</t>
+  </si>
+  <si>
+    <t>Checked against NCIS linked mortality files (LMFs), and the variables dodqtr and dodyear are present but all NA. The NHANES portion of the script provided online (https://www.cdc.gov/nchs/linked-data/mortality-files/index.html, R_ReadInProgramAllSurveys) does not include dodqtr and dodyr. Considered these unavailable.</t>
+  </si>
+  <si>
+    <t>paste</t>
+  </si>
+  <si>
+    <t>direct_mapping</t>
+  </si>
+  <si>
+    <t>"NHANES"</t>
+  </si>
+  <si>
+    <t>"NHANES_2011"</t>
+  </si>
+  <si>
+    <t>"United States"</t>
+  </si>
+  <si>
+    <t>Added in updated DataSchema.</t>
+  </si>
+  <si>
+    <t>dth_cancer_nhanes added, so removed cancer from the coding in this variable.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -328,7 +417,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +427,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,34 +449,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,674 +815,946 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A96D0D0-036F-4639-8FBF-4A4CEF797E7C}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="85.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="27.42578125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="43.5703125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21" style="5" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="27.85546875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="24.42578125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="57.42578125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="22.28515625" style="4" customWidth="1"/>
-    <col min="20" max="20" width="29.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.28515625" style="4" customWidth="1"/>
-    <col min="22" max="16384" width="11.5703125" style="4"/>
+    <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.5703125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="21" style="4" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" style="4" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" style="4" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="33.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="18.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="16.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="57.42578125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="22.28515625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="29.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.28515625" style="3" customWidth="1"/>
+    <col min="22" max="16384" width="11.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>76</v>
+      <c r="T1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R6" s="3">
+        <v>2019</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R7" s="4">
+        <v>12</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="F11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M11" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R11" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="5" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="B22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="S5" s="4" t="s">
+      <c r="F22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="T5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="M22" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O7" s="4" t="s">
+      <c r="O22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Q7" s="5" t="s">
+      <c r="Q22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="R7" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>70</v>
+      <c r="R22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/linkage/data_processing_elements_linkage-NHANES11.xlsx
+++ b/linkage/data_processing_elements_linkage-NHANES11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1225266-3537-44C6-8B5B-E0A79E170672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626D65C6-0812-4F30-B76C-B7AB2D998845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
+    <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -152,9 +152,6 @@
     <t>Accidents (Unintentional Injuries) NHANES - ICD10: V01–X59, Y85–Y86</t>
   </si>
   <si>
-    <t>adm_id</t>
-  </si>
-  <si>
     <t>ICD10 codes for the causes of death are present in the database in the most detailed format (e.g., C169)</t>
   </si>
   <si>
@@ -366,6 +363,9 @@
   </si>
   <si>
     <t>dth_cancer_nhanes added, so removed cancer from the coding in this variable.</t>
+  </si>
+  <si>
+    <t>adm_participant</t>
   </si>
 </sst>
 </file>
@@ -898,13 +898,13 @@
         <v>16</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -912,10 +912,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>74</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>28</v>
@@ -924,22 +924,22 @@
         <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -947,37 +947,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -985,37 +985,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q4" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -1023,37 +1023,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q5" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U5" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1061,37 +1061,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q6" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R6" s="3">
         <v>2019</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -1099,37 +1099,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q7" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R7" s="4">
         <v>12</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1137,43 +1137,43 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="O8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="Q8" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -1181,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>22</v>
@@ -1193,31 +1193,31 @@
         <v>17</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="Q9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -1225,7 +1225,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>20</v>
@@ -1237,31 +1237,31 @@
         <v>17</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="U10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -1269,7 +1269,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>18</v>
@@ -1281,25 +1281,25 @@
         <v>17</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P11" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="Q11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -1307,37 +1307,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="Q12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1345,10 +1345,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>29</v>
@@ -1357,28 +1357,28 @@
         <v>17</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="R13" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1386,43 +1386,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P14" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1430,10 +1430,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>30</v>
@@ -1442,28 +1442,28 @@
         <v>17</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>31</v>
@@ -1483,28 +1483,28 @@
         <v>17</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P16" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1512,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>24</v>
@@ -1524,28 +1524,28 @@
         <v>17</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P17" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1553,10 +1553,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>33</v>
@@ -1565,28 +1565,28 @@
         <v>17</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P18" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1594,10 +1594,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>34</v>
@@ -1606,28 +1606,28 @@
         <v>17</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P19" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1635,10 +1635,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>35</v>
@@ -1647,28 +1647,28 @@
         <v>17</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P20" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="45" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>36</v>
@@ -1688,28 +1688,28 @@
         <v>17</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P21" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="30" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>25</v>
@@ -1729,28 +1729,28 @@
         <v>17</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/linkage/data_processing_elements_linkage-NHANES11.xlsx
+++ b/linkage/data_processing_elements_linkage-NHANES11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626D65C6-0812-4F30-B76C-B7AB2D998845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303EFC36-CC09-48C3-92D3-FE08196CF368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
   </bookViews>
@@ -365,7 +365,7 @@
     <t>dth_cancer_nhanes added, so removed cancer from the coding in this variable.</t>
   </si>
   <si>
-    <t>adm_participant</t>
+    <t>adm_participant_id</t>
   </si>
 </sst>
 </file>
